--- a/Project Documents/MASTER/Supervisor Master.xlsx
+++ b/Project Documents/MASTER/Supervisor Master.xlsx
@@ -769,6 +769,7 @@
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.85546875" customWidth="1"/>
+    <col min="9" max="9" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
